--- a/Data/Partidos.xlsx
+++ b/Data/Partidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancolombia-my.sharepoint.com/personal/damonsal_bancolombia_com_co/Documents/Reto_mundial/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{F81A0260-9995-4DE4-B3BB-7C29FAC3BA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BEF5215-FCDE-4480-9361-7B548E4ADC44}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{F81A0260-9995-4DE4-B3BB-7C29FAC3BA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932DC8E6-DAC5-4FAF-9E98-46A17DB0A8B9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{26C8A8AA-C5DC-4E3D-96D5-1B57BBE38D7D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{26C8A8AA-C5DC-4E3D-96D5-1B57BBE38D7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -212,21 +212,12 @@
     <t>11 de junio de 2026</t>
   </si>
   <si>
-    <t>Ganador Play-off D UEFA</t>
-  </si>
-  <si>
-    <t>Ganador Play-off A UEFA</t>
-  </si>
-  <si>
     <t>12 de junio de 2026</t>
   </si>
   <si>
     <t>13 de junio de 2026</t>
   </si>
   <si>
-    <t>Ganador Play-off C UEFA</t>
-  </si>
-  <si>
     <t>Fase de Grues</t>
   </si>
   <si>
@@ -236,9 +227,6 @@
     <t>14 de junio de 2026</t>
   </si>
   <si>
-    <t>Ganador Play-off B UEFA</t>
-  </si>
-  <si>
     <t>15 de junio de 2026</t>
   </si>
   <si>
@@ -248,12 +236,6 @@
     <t>16 de junio de 2026</t>
   </si>
   <si>
-    <t>Ganador Play-off Intercont. 2</t>
-  </si>
-  <si>
-    <t>Ganador Play-off Intercont. 1</t>
-  </si>
-  <si>
     <t>17 de junio de 2026</t>
   </si>
   <si>
@@ -546,6 +528,24 @@
   </si>
   <si>
     <t>19 de julio de 2026</t>
+  </si>
+  <si>
+    <t>Chequia</t>
+  </si>
+  <si>
+    <t>Bosnia y H.</t>
+  </si>
+  <si>
+    <t>Turquía</t>
+  </si>
+  <si>
+    <t>DR Congo</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>Iraq</t>
   </si>
 </sst>
 </file>
@@ -595,7 +595,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -993,7 +993,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>57</v>
@@ -1011,10 +1011,10 @@
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -1032,7 +1032,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" s="2"/>
     </row>
@@ -1050,7 +1050,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -1065,10 +1065,10 @@
         <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -1086,25 +1086,25 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H9" s="2"/>
     </row>
@@ -1122,7 +1122,7 @@
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -1140,7 +1140,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -1158,7 +1158,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -1170,13 +1170,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -1194,7 +1194,7 @@
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -1206,13 +1206,13 @@
         <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -1230,7 +1230,7 @@
         <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2"/>
     </row>
@@ -1248,7 +1248,7 @@
         <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H17" s="2"/>
     </row>
@@ -1266,7 +1266,7 @@
         <v>42</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H18" s="2"/>
     </row>
@@ -1278,13 +1278,13 @@
         <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -1302,7 +1302,7 @@
         <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H20" s="2"/>
     </row>
@@ -1320,7 +1320,7 @@
         <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H21" s="2"/>
     </row>
@@ -1335,10 +1335,10 @@
         <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H22" s="2"/>
     </row>
@@ -1356,7 +1356,7 @@
         <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H23" s="2"/>
     </row>
@@ -1368,13 +1368,13 @@
         <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H24" s="2"/>
     </row>
@@ -1392,7 +1392,7 @@
         <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H25" s="2"/>
     </row>
@@ -1404,13 +1404,13 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H26" s="2"/>
     </row>
@@ -1425,10 +1425,10 @@
         <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H27" s="2"/>
     </row>
@@ -1443,10 +1443,10 @@
         <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H28" s="2"/>
     </row>
@@ -1464,7 +1464,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H29" s="2"/>
     </row>
@@ -1482,7 +1482,7 @@
         <v>21</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H30" s="2"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H31" s="2"/>
     </row>
@@ -1518,7 +1518,7 @@
         <v>19</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H32" s="2"/>
     </row>
@@ -1530,13 +1530,13 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H33" s="2"/>
     </row>
@@ -1551,10 +1551,10 @@
         <v>26</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H34" s="2"/>
     </row>
@@ -1572,7 +1572,7 @@
         <v>28</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H35" s="2"/>
     </row>
@@ -1590,7 +1590,7 @@
         <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H36" s="2"/>
     </row>
@@ -1608,7 +1608,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H37" s="2"/>
     </row>
@@ -1623,10 +1623,10 @@
         <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H38" s="2"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>38</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H39" s="2"/>
     </row>
@@ -1662,7 +1662,7 @@
         <v>33</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H40" s="2"/>
     </row>
@@ -1680,7 +1680,7 @@
         <v>36</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H41" s="2"/>
     </row>
@@ -1698,7 +1698,7 @@
         <v>47</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H42" s="2"/>
     </row>
@@ -1713,10 +1713,10 @@
         <v>41</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H43" s="2"/>
     </row>
@@ -1734,7 +1734,7 @@
         <v>42</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H44" s="2"/>
     </row>
@@ -1752,7 +1752,7 @@
         <v>46</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -1770,7 +1770,7 @@
         <v>52</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H46" s="2"/>
     </row>
@@ -1785,10 +1785,10 @@
         <v>54</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="H47" s="2"/>
     </row>
@@ -1806,7 +1806,7 @@
         <v>55</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H48" s="2"/>
     </row>
@@ -1821,10 +1821,10 @@
         <v>50</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H49" s="2"/>
     </row>
@@ -1842,7 +1842,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H50" s="2"/>
     </row>
@@ -1854,13 +1854,13 @@
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H51" s="2"/>
     </row>
@@ -1878,7 +1878,7 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H52" s="2"/>
     </row>
@@ -1896,7 +1896,7 @@
         <v>19</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H53" s="2"/>
     </row>
@@ -1908,13 +1908,13 @@
         <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H54" s="2"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>9</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H55" s="2"/>
     </row>
@@ -1950,7 +1950,7 @@
         <v>23</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H56" s="2"/>
     </row>
@@ -1968,7 +1968,7 @@
         <v>28</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" s="2"/>
     </row>
@@ -1986,7 +1986,7 @@
         <v>26</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H58" s="2"/>
     </row>
@@ -2001,10 +2001,10 @@
         <v>27</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H59" s="2"/>
     </row>
@@ -2016,13 +2016,13 @@
         <v>12</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H60" s="2"/>
     </row>
@@ -2040,7 +2040,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H61" s="2"/>
     </row>
@@ -2058,7 +2058,7 @@
         <v>41</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H62" s="2"/>
     </row>
@@ -2073,10 +2073,10 @@
         <v>42</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H63" s="2"/>
     </row>
@@ -2094,7 +2094,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H64" s="2"/>
     </row>
@@ -2112,7 +2112,7 @@
         <v>35</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H65" s="2"/>
     </row>
@@ -2127,10 +2127,10 @@
         <v>33</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -2147,7 +2147,7 @@
         <v>32</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
@@ -2164,7 +2164,7 @@
         <v>54</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
@@ -2178,10 +2178,10 @@
         <v>55</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
@@ -2198,7 +2198,7 @@
         <v>47</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
@@ -2215,7 +2215,7 @@
         <v>45</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
@@ -2232,7 +2232,7 @@
         <v>51</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
@@ -2243,557 +2243,557 @@
         <v>49</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B74" s="2">
         <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B75" s="2">
         <v>74</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B76" s="2">
         <v>75</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B77" s="2">
         <v>76</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B78" s="2">
         <v>77</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2">
         <v>78</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="E79" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B80" s="2">
         <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B81" s="2">
         <v>80</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B82" s="2">
         <v>81</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B83" s="2">
         <v>82</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B84" s="2">
         <v>83</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B85" s="2">
         <v>84</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B86" s="2">
         <v>85</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B87" s="2">
         <v>86</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B88" s="2">
         <v>87</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B89" s="2">
         <v>88</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B90" s="2">
         <v>89</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B91" s="2">
         <v>90</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B92" s="2">
         <v>91</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B93" s="2">
         <v>92</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B94" s="2">
         <v>93</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B95" s="2">
         <v>94</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B96" s="2">
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B97" s="2">
         <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B98" s="2">
         <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B99" s="2">
         <v>98</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B100" s="2">
         <v>99</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B101" s="2">
         <v>100</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B102" s="2">
         <v>101</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B103" s="2">
         <v>102</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B104" s="2">
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B105" s="2">
         <v>104</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
